--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA6FDF2-6696-AB47-8B30-4EF324CFACEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2567E296-0D84-2A43-A1BD-8284B050907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,15 @@
   <si>
     <t>August</t>
   </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>A divinely boring day overall. 7 out of 8 lectures were boring, making the day feel endless.</t>
+  </si>
 </sst>
 </file>
 
@@ -227,73 +236,73 @@
       <sz val="18"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -875,7 +884,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -1048,27 +1057,51 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14" t="str">
+    <row r="7" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="12">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="13">
+        <v>460</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13">
+        <v>60</v>
+      </c>
+      <c r="E7" s="13">
+        <v>60</v>
+      </c>
+      <c r="F7" s="13">
+        <v>400</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="H7" s="13">
+        <v>120</v>
+      </c>
+      <c r="I7" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="14" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J7" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2567E296-0D84-2A43-A1BD-8284B050907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465A96BE-6573-A340-8B5B-C4293B43C568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,18 @@
   <si>
     <t>A divinely boring day overall. 7 out of 8 lectures were boring, making the day feel endless.</t>
   </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Today was a genuinely nice day. The lectures felt engaging, the atmosphere was pleasant, and overall the day passed by smoothly. After yesterday’s endless lectures, today was a refreshing change and left me in a much better mood.</t>
+  </si>
 </sst>
 </file>
 
@@ -223,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +330,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -366,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -413,6 +431,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,31 +1120,55 @@
       <c r="M7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14" t="str">
+    <row r="8" spans="1:14" ht="128" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="13">
+        <v>300</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>120</v>
+      </c>
+      <c r="E8" s="13">
+        <v>60</v>
+      </c>
+      <c r="F8" s="13">
+        <v>350</v>
+      </c>
+      <c r="G8" s="13">
+        <v>7</v>
+      </c>
+      <c r="H8" s="13">
+        <v>300</v>
+      </c>
+      <c r="I8" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="14" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J8" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
+        <v>310</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465A96BE-6573-A340-8B5B-C4293B43C568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704DEF51-4129-9442-AF3B-0A8EC416B2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>Today was a genuinely nice day. The lectures felt engaging, the atmosphere was pleasant, and overall the day passed by smoothly. After yesterday’s endless lectures, today was a refreshing change and left me in a much better mood.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Went along with my friends to wagha border so see parade on independence day.</t>
   </si>
 </sst>
 </file>
@@ -428,12 +434,12 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,74 +925,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12600351</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
@@ -1120,7 +1126,7 @@
       <c r="M7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="19" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1170,27 +1176,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14" t="str">
+    <row r="9" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="12">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="13">
+        <v>480</v>
+      </c>
+      <c r="C9" s="13">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
+        <v>900</v>
+      </c>
+      <c r="I9" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="14" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J9" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704DEF51-4129-9442-AF3B-0A8EC416B2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF1EA47-25B9-5046-AE55-4828283DCE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>Went along with my friends to wagha border so see parade on independence day.</t>
+  </si>
+  <si>
+    <t>156/08/2026</t>
+  </si>
+  <si>
+    <t>Did some DSA, and worked on a npm package.</t>
   </si>
 </sst>
 </file>
@@ -1222,27 +1228,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14" t="str">
+    <row r="10" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="13">
+        <v>480</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13">
+        <v>180</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>600</v>
+      </c>
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="14" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF1EA47-25B9-5046-AE55-4828283DCE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC97C33-19EF-D74E-84A5-5E806135972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -234,10 +234,10 @@
     <t>Went along with my friends to wagha border so see parade on independence day.</t>
   </si>
   <si>
-    <t>156/08/2026</t>
+    <t>Did some DSA, and worked on a npm package.</t>
   </si>
   <si>
-    <t>Did some DSA, and worked on a npm package.</t>
+    <t>Did some DSA.</t>
   </si>
 </sst>
 </file>
@@ -1229,8 +1229,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>65</v>
+      <c r="A10" s="12">
+        <v>46250</v>
       </c>
       <c r="B10" s="13">
         <v>480</v>
@@ -1271,30 +1271,54 @@
         <v>57</v>
       </c>
       <c r="N10" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="12">
+        <v>46251</v>
+      </c>
+      <c r="B11" s="13">
+        <v>480</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>180</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <v>600</v>
+      </c>
+      <c r="I11" s="14">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J11" s="14">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="16" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC97C33-19EF-D74E-84A5-5E806135972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E919EA65-EE86-AD4F-82FB-E03FCF86DF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Did some DSA.</t>
+  </si>
+  <si>
+    <t>Too many lectures with less sleep drained all energy.</t>
   </si>
 </sst>
 </file>
@@ -1320,27 +1323,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14" t="str">
+    <row r="12" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
+        <v>46252</v>
+      </c>
+      <c r="B12" s="13">
+        <v>400</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>120</v>
+      </c>
+      <c r="E12" s="13">
+        <v>60</v>
+      </c>
+      <c r="F12" s="13">
+        <v>400</v>
+      </c>
+      <c r="G12" s="13">
+        <v>8</v>
+      </c>
+      <c r="H12" s="13">
+        <v>350</v>
+      </c>
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="14" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E919EA65-EE86-AD4F-82FB-E03FCF86DF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC2AADD-9745-6345-8CD1-67E49CEBF2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>Too many lectures with less sleep drained all energy.</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Updated Resume and Portfolio</t>
   </si>
 </sst>
 </file>
@@ -1369,27 +1375,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14" t="str">
+    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="12">
+        <v>46253</v>
+      </c>
+      <c r="B13" s="13">
+        <v>450</v>
+      </c>
+      <c r="C13" s="13">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13">
+        <v>90</v>
+      </c>
+      <c r="E13" s="13">
+        <v>200</v>
+      </c>
+      <c r="F13" s="13">
+        <v>200</v>
+      </c>
+      <c r="G13" s="13">
+        <v>4</v>
+      </c>
+      <c r="H13" s="13">
+        <v>450</v>
+      </c>
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="14" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC2AADD-9745-6345-8CD1-67E49CEBF2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C224A467-9300-5F4C-980C-382C8BE8E364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>Updated Resume and Portfolio</t>
+  </si>
+  <si>
+    <t>Did a whole bunch of DSA.</t>
   </si>
 </sst>
 </file>
@@ -1421,27 +1424,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14" t="str">
+    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
+        <v>46254</v>
+      </c>
+      <c r="B14" s="13">
+        <v>420</v>
+      </c>
+      <c r="C14" s="13">
+        <v>30</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <v>150</v>
+      </c>
+      <c r="F14" s="13">
+        <v>300</v>
+      </c>
+      <c r="G14" s="13">
+        <v>6</v>
+      </c>
+      <c r="H14" s="13">
+        <v>310</v>
+      </c>
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="14" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J14" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C224A467-9300-5F4C-980C-382C8BE8E364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D890E803-EB6A-E54F-9731-AE6C30B20ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Did a whole bunch of DSA.</t>
+  </si>
+  <si>
+    <t>Learned Manacher's Algorithm</t>
   </si>
 </sst>
 </file>
@@ -1470,27 +1473,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14" t="str">
+    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="12">
+        <v>46255</v>
+      </c>
+      <c r="B15" s="13">
+        <v>420</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <v>230</v>
+      </c>
+      <c r="F15" s="13">
+        <v>300</v>
+      </c>
+      <c r="G15" s="13">
+        <v>6</v>
+      </c>
+      <c r="H15" s="13">
+        <v>350</v>
+      </c>
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="14" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J15" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D890E803-EB6A-E54F-9731-AE6C30B20ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0981C1A2-FD34-E04D-8561-72DAB23BBFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Learned Manacher's Algorithm</t>
+  </si>
+  <si>
+    <t>Learned Floyd's Cycle Detection and Manacher's Algorithm</t>
   </si>
 </sst>
 </file>
@@ -1519,27 +1522,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14" t="str">
+    <row r="16" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="13">
+        <v>450</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>100</v>
+      </c>
+      <c r="E16" s="13">
+        <v>670</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>220</v>
+      </c>
+      <c r="I16" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="14" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J16" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0981C1A2-FD34-E04D-8561-72DAB23BBFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9358C64-A0ED-F74D-BEC2-DEDC3D6A6C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>Learned Floyd's Cycle Detection and Manacher's Algorithm</t>
+  </si>
+  <si>
+    <t>Learmed Advanced SQL and Revisied Complete Syntax of C++.</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1539,7 @@
         <v>100</v>
       </c>
       <c r="E16" s="13">
-        <v>670</v>
+        <v>470</v>
       </c>
       <c r="F16" s="13">
         <v>0</v>
@@ -1545,15 +1548,15 @@
         <v>0</v>
       </c>
       <c r="H16" s="13">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="I16" s="14">
         <f t="shared" si="0"/>
-        <v>1440</v>
+        <v>1340</v>
       </c>
       <c r="J16" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>59</v>
@@ -1568,27 +1571,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14" t="str">
+    <row r="17" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="12">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="13">
+        <v>450</v>
+      </c>
+      <c r="C17" s="13">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
+        <v>220</v>
+      </c>
+      <c r="E17" s="13">
+        <v>500</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>150</v>
+      </c>
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="14" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J17" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="16" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9358C64-A0ED-F74D-BEC2-DEDC3D6A6C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D65BF3-6B3F-D642-A8F9-DE4229299910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Learmed Advanced SQL and Revisied Complete Syntax of C++.</t>
+  </si>
+  <si>
+    <t>Did some DSA and Database Exercises.</t>
   </si>
 </sst>
 </file>
@@ -1617,27 +1620,49 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+    <row r="18" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="12">
+        <v>46258</v>
+      </c>
       <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14" t="str">
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <v>180</v>
+      </c>
+      <c r="E18" s="13">
+        <v>200</v>
+      </c>
+      <c r="F18" s="13">
+        <v>150</v>
+      </c>
+      <c r="G18" s="13">
+        <v>3</v>
+      </c>
+      <c r="H18" s="13">
+        <v>500</v>
+      </c>
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J18" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D65BF3-6B3F-D642-A8F9-DE4229299910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1FCE43-7AA4-234E-B6D8-065A1C0D50EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Did some DSA and Database Exercises.</t>
+  </si>
+  <si>
+    <t>Attended a bunch of classes and Learned C++.</t>
   </si>
 </sst>
 </file>
@@ -1624,7 +1627,9 @@
       <c r="A18" s="12">
         <v>46258</v>
       </c>
-      <c r="B18" s="13"/>
+      <c r="B18" s="13">
+        <v>400</v>
+      </c>
       <c r="C18" s="13">
         <v>0</v>
       </c>
@@ -1645,11 +1650,11 @@
       </c>
       <c r="I18" s="14">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1430</v>
       </c>
       <c r="J18" s="14">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>59</v>
@@ -1664,27 +1669,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14" t="str">
+    <row r="19" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="12">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="13">
+        <v>450</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13">
+        <v>180</v>
+      </c>
+      <c r="E19" s="13">
+        <v>60</v>
+      </c>
+      <c r="F19" s="13">
+        <v>350</v>
+      </c>
+      <c r="G19" s="13">
+        <v>7</v>
+      </c>
+      <c r="H19" s="13">
+        <v>300</v>
+      </c>
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="14" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1FCE43-7AA4-234E-B6D8-065A1C0D50EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2741EB-5CEC-3E4E-A3B7-D2E0106A8814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Attended a bunch of classes and Learned C++.</t>
+  </si>
+  <si>
+    <t>Learned Prefix Sum Pattern.</t>
   </si>
 </sst>
 </file>
@@ -1715,27 +1718,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+    <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="12">
+        <v>46260</v>
+      </c>
       <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14" t="str">
+      <c r="C20" s="13">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
+        <v>70</v>
+      </c>
+      <c r="E20" s="13">
+        <v>200</v>
+      </c>
+      <c r="F20" s="13">
+        <v>200</v>
+      </c>
+      <c r="G20" s="13">
+        <v>4</v>
+      </c>
+      <c r="H20" s="13">
+        <v>450</v>
+      </c>
+      <c r="I20" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="14" t="str">
+        <v>920</v>
+      </c>
+      <c r="J20" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2741EB-5CEC-3E4E-A3B7-D2E0106A8814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D9E7A0-F7C1-AB4A-A10E-AA7E24B54F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Learned Prefix Sum Pattern.</t>
+  </si>
+  <si>
+    <t>Did DSA problems, average day.</t>
   </si>
 </sst>
 </file>
@@ -1762,27 +1765,49 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
+    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="12">
+        <v>46261</v>
+      </c>
       <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14" t="str">
+      <c r="C21" s="13">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <v>60</v>
+      </c>
+      <c r="E21" s="13">
+        <v>300</v>
+      </c>
+      <c r="F21" s="13">
+        <v>350</v>
+      </c>
+      <c r="G21" s="13">
+        <v>7</v>
+      </c>
+      <c r="H21" s="13">
+        <v>450</v>
+      </c>
+      <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="14" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D9E7A0-F7C1-AB4A-A10E-AA7E24B54F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADD9C12-8C52-9842-8692-DCF8D17B6005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Did DSA problems, average day.</t>
+  </si>
+  <si>
+    <t>RakshaBandhan</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1728,9 @@
       <c r="A20" s="12">
         <v>46260</v>
       </c>
-      <c r="B20" s="13"/>
+      <c r="B20" s="13">
+        <v>480</v>
+      </c>
       <c r="C20" s="13">
         <v>0</v>
       </c>
@@ -1746,11 +1751,11 @@
       </c>
       <c r="I20" s="14">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1400</v>
       </c>
       <c r="J20" s="14">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>40</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>52</v>
@@ -1769,7 +1774,9 @@
       <c r="A21" s="12">
         <v>46261</v>
       </c>
-      <c r="B21" s="13"/>
+      <c r="B21" s="13">
+        <v>480</v>
+      </c>
       <c r="C21" s="13">
         <v>0</v>
       </c>
@@ -1786,15 +1793,15 @@
         <v>7</v>
       </c>
       <c r="H21" s="13">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="I21" s="14">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1390</v>
       </c>
       <c r="J21" s="14">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>50</v>
       </c>
       <c r="K21" s="15" t="s">
         <v>59</v>
@@ -1809,27 +1816,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14" t="str">
+    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="12">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="13">
+        <v>480</v>
+      </c>
+      <c r="C22" s="13">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
+        <v>250</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
+        <v>700</v>
+      </c>
+      <c r="I22" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="14" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J22" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADD9C12-8C52-9842-8692-DCF8D17B6005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2EB58C-95D9-4244-843C-481E489E5F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1862,27 +1862,51 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14" t="str">
+    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="12">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="13">
+        <v>450</v>
+      </c>
+      <c r="C23" s="13">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13">
+        <v>450</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>300</v>
+      </c>
+      <c r="I23" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="14" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2EB58C-95D9-4244-843C-481E489E5F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B52953-4A43-DE4C-9A59-84D1C5DDD407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1908,27 +1908,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14" t="str">
+    <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="12">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="13">
+        <v>460</v>
+      </c>
+      <c r="C24" s="13">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <v>100</v>
+      </c>
+      <c r="E24" s="13">
+        <v>560</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13">
+        <v>280</v>
+      </c>
+      <c r="I24" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J24" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B52953-4A43-DE4C-9A59-84D1C5DDD407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A083F6-D248-E043-B38D-1D87EE1B4B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>RakshaBandhan</t>
+  </si>
+  <si>
+    <t>Learned Complete SQL for RPL exam.</t>
   </si>
 </sst>
 </file>
@@ -1954,27 +1957,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14" t="str">
+    <row r="25" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="13">
+        <v>480</v>
+      </c>
+      <c r="C25" s="13">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13">
+        <v>320</v>
+      </c>
+      <c r="E25" s="13">
+        <v>410</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
+        <v>100</v>
+      </c>
+      <c r="I25" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J25" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A083F6-D248-E043-B38D-1D87EE1B4B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858844DE-98B6-E04C-9630-98A89DF1C7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Learned Complete SQL for RPL exam.</t>
+  </si>
+  <si>
+    <t>Started Solving Frontend Problems asked by FANG Companies.</t>
   </si>
 </sst>
 </file>
@@ -2003,27 +2006,51 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14" t="str">
+    <row r="26" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="12">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="13">
+        <v>390</v>
+      </c>
+      <c r="C26" s="13">
+        <v>0</v>
+      </c>
+      <c r="D26" s="13">
+        <v>150</v>
+      </c>
+      <c r="E26" s="13">
+        <v>370</v>
+      </c>
+      <c r="F26" s="13">
+        <v>350</v>
+      </c>
+      <c r="G26" s="13">
+        <v>7</v>
+      </c>
+      <c r="H26" s="13">
+        <v>100</v>
+      </c>
+      <c r="I26" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J26" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858844DE-98B6-E04C-9630-98A89DF1C7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EECA16D-0573-ED4D-B32C-4C67AD0BAF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Started Solving Frontend Problems asked by FANG Companies.</t>
+  </si>
+  <si>
+    <t>Solved DSA and Frontend Questions.</t>
   </si>
 </sst>
 </file>
@@ -2052,27 +2055,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14" t="str">
+    <row r="27" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="12">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="13">
+        <v>400</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <v>200</v>
+      </c>
+      <c r="E27" s="13">
+        <v>250</v>
+      </c>
+      <c r="F27" s="13">
+        <v>200</v>
+      </c>
+      <c r="G27" s="13">
+        <v>4</v>
+      </c>
+      <c r="H27" s="13">
+        <v>310</v>
+      </c>
+      <c r="I27" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="14" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J27" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EECA16D-0573-ED4D-B32C-4C67AD0BAF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C4ACFA-9253-F74F-87B8-313910668879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2101,27 +2101,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14" t="str">
+    <row r="28" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="12">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="13">
+        <v>400</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
+        <v>100</v>
+      </c>
+      <c r="E28" s="13">
+        <v>260</v>
+      </c>
+      <c r="F28" s="13">
+        <v>350</v>
+      </c>
+      <c r="G28" s="13">
+        <v>7</v>
+      </c>
+      <c r="H28" s="13">
+        <v>200</v>
+      </c>
+      <c r="I28" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J28" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C4ACFA-9253-F74F-87B8-313910668879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1092ADD-6ACD-E04C-86C5-747604DE72E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Solved DSA and Frontend Questions.</t>
+  </si>
+  <si>
+    <t>Went to watch Mirzapur with friends.</t>
   </si>
 </sst>
 </file>
@@ -2147,27 +2150,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14" t="str">
+    <row r="29" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="12">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="13">
+        <v>400</v>
+      </c>
+      <c r="C29" s="13">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
+        <v>100</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
+        <v>300</v>
+      </c>
+      <c r="G29" s="13">
+        <v>6</v>
+      </c>
+      <c r="H29" s="13">
+        <v>210</v>
+      </c>
+      <c r="I29" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="14" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J29" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>

--- a/12600351.xlsx
+++ b/12600351.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sage/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1092ADD-6ACD-E04C-86C5-747604DE72E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3F4648-3AB5-934D-BB31-B9DCB32894E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>Went to watch Mirzapur with friends.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Solved Some two pointer Questions.</t>
   </si>
 </sst>
 </file>
@@ -2196,27 +2202,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14" t="str">
+    <row r="30" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A30" s="12">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="13">
+        <v>320</v>
+      </c>
+      <c r="C30" s="13">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <v>0</v>
+      </c>
+      <c r="E30" s="13">
+        <v>200</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
+        <v>600</v>
+      </c>
+      <c r="I30" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J30" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
